--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,39 +455,9 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.644</v>
+        <v>2.999</v>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.774</v>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -504,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,9 +501,54 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.999</v>
+        <v>3.051</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -550,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +592,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.051</v>
+        <v>2.644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -592,7 +607,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.207</v>
+        <v>2.742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -607,24 +622,9 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.239</v>
+        <v>2.774</v>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="In-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Co-In" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +452,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.999</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -474,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,11 +558,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.051</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -512,45 +573,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.207</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -588,41 +619,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.644</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.742</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.774</v>
+        <v>3.294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -664,15 +695,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.975</v>
+        <v>2.964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="In-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="In-In" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Co-In" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,11 +562,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -582,6 +582,21 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -596,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,11 +638,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -643,21 +658,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="In-In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Co-In" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="In-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -471,54 +471,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -535,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,11 +517,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -577,11 +532,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>deficiency_no_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -592,11 +547,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.294</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -611,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,11 +623,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -658,6 +643,21 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="In-In" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -471,9 +471,54 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -490,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,11 +562,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -532,11 +577,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -547,41 +592,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>3.294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -596,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,11 +638,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -643,21 +658,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -8,10 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.055</v>
+        <v>3.004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -535,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,11 +560,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -582,21 +580,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -611,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,11 +621,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -661,95 +644,33 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="In-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="In-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -469,54 +469,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.004</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>
@@ -533,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,11 +515,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -580,6 +535,36 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -594,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,11 +606,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.004</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -636,11 +621,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>deficiency_no_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -651,11 +636,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.27</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency_no_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -666,11 +651,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.294</v>
+        <v>2.742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -474,6 +474,36 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -488,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,11 +545,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.004</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -530,11 +560,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>deficiency_no_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -545,11 +575,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.27</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency_no_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -560,11 +590,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.294</v>
+        <v>2.742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
         </is>
       </c>
     </row>
@@ -579,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,7 +651,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -621,54 +666,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.004</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>full_occupancy_atomic_mixing</t>
         </is>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,56 +456,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.004</v>
+        <v>2.964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
+          <t>deficiency</t>
         </is>
       </c>
     </row>
@@ -605,7 +562,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.004</v>
+        <v>3.055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -624,6 +581,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +454,56 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.964</v>
+        <v>3.004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
         </is>
       </c>
     </row>
@@ -562,7 +605,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.055</v>
+        <v>3.004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -581,128 +624,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +456,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.004</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -469,11 +471,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -484,11 +486,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.27</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -499,13 +501,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.294</v>
+        <v>2.742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -545,11 +589,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -560,58 +604,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
+        <v>3.104</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.004</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+        <v>0.135</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -624,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,11 +677,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -670,9 +696,193 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.183</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20240325_Er/output/20240325_Er_site_pairs.xlsx
+++ b/20240325_Er/output/20240325_Er_site_pairs.xlsx
@@ -8,10 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.055</v>
+        <v>3.004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -536,7 +534,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.762</v>
+        <v>2.752</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -547,7 +545,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.171</v>
+        <v>0.149</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -562,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +587,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -613,31 +611,61 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>3.104</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B7" t="n">
+        <v>3.192</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -650,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,11 +705,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -701,188 +729,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.104</v>
+      </c>
       <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.183</v>
+        <v>0.135</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1814810.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
